--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487968_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487968_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4572</v>
+        <v>5.7987</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7988</v>
+        <v>6.2172</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6584</v>
+        <v>-0.4186</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9334</v>
+        <v>5.1364</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0852</v>
+        <v>-1.3667</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8482</v>
+        <v>6.5031</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2853</v>
+        <v>5.4334</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6709</v>
+        <v>-0.6451</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6143</v>
+        <v>6.0785</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6481</v>
+        <v>-0.297</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5857</v>
+        <v>-0.7215</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2338</v>
+        <v>0.4246</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3964</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q2" t="n">
         <v>-2.1805</v>
       </c>
       <c r="R2" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1195</v>
+        <v>0.1202</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5573</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5621</v>
+        <v>-0.5003</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1992</v>
+        <v>1.1367</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1367</v>
+        <v>2.3438</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3359</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7891</v>
+        <v>5.5237</v>
       </c>
       <c r="E3" t="n">
-        <v>5.685</v>
+        <v>4.09</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8959</v>
+        <v>1.4338</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1364</v>
+        <v>3.9334</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3667</v>
+        <v>2.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5031</v>
+        <v>1.8482</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4334</v>
+        <v>3.2853</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6451</v>
+        <v>2.6709</v>
       </c>
       <c r="L3" t="n">
-        <v>6.0785</v>
+        <v>0.6143</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.297</v>
+        <v>0.6481</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7215</v>
+        <v>-0.5857</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4246</v>
+        <v>1.2338</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.1805</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8894</v>
+        <v>2.186</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0883</v>
+        <v>1.8485</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9776</v>
+        <v>0.3375</v>
       </c>
       <c r="V3" t="n">
+        <v>-0.1992</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.1367</v>
       </c>
-      <c r="W3" t="n">
-        <v>2.3438</v>
-      </c>
       <c r="X3" t="n">
-        <v>-1.2071</v>
+        <v>-1.3359</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.198</v>
+        <v>1.088</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9154</v>
+        <v>1.4684</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7174</v>
+        <v>-0.3805</v>
       </c>
       <c r="G4" t="n">
         <v>0.0269</v>
@@ -766,13 +766,13 @@
         <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8341</v>
+        <v>0.7241</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5603</v>
+        <v>1.1133</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7262</v>
+        <v>-0.3892</v>
       </c>
       <c r="V4" t="n">
         <v>0.337</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8689</v>
+        <v>1.0089</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9539</v>
+        <v>-1.1799</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8228</v>
+        <v>2.1888</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.8907</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.8376</v>
+        <v>-4.038</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9469</v>
+        <v>4.1248</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.5841</v>
+        <v>-0.2315</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.7047</v>
+        <v>-2.8509</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1205</v>
+        <v>2.6193</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3066</v>
+        <v>0.3184</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1329</v>
+        <v>-1.1871</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8264</v>
+        <v>1.5055</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>-3.1716</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="S5" t="n">
-        <v>2.612</v>
+        <v>1.0352</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8811</v>
+        <v>1.0161</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7309</v>
+        <v>0.019</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1476</v>
+        <v>1.2745</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7403</v>
+        <v>1.2071</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4074</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7045</v>
+        <v>0.8792</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0116</v>
+        <v>2.074</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3071</v>
+        <v>-1.1948</v>
       </c>
       <c r="G6" t="n">
         <v>1.1122</v>
@@ -922,13 +922,13 @@
         <v>0.7929</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1373</v>
+        <v>0.312</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3892</v>
+        <v>0.4516</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2519</v>
+        <v>-0.1396</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1397</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3472</v>
+        <v>0.039</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8057</v>
+        <v>-1.8291</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1529</v>
+        <v>1.8681</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6569</v>
+        <v>-3.8907</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3298</v>
+        <v>-4.8376</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3271</v>
+        <v>0.9469</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8643</v>
+        <v>-3.5841</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3386</v>
+        <v>-3.7047</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4744</v>
+        <v>0.1205</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5212</v>
+        <v>-0.3066</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6684</v>
+        <v>-1.1329</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1472</v>
+        <v>0.8264</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
         <v>0.9911</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0499</v>
+        <v>1.7821</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1396</v>
+        <v>1.0059</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0897</v>
+        <v>0.7762</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5331</v>
+        <v>2.1476</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5331</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4039</v>
+        <v>-0.0915</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2839</v>
+        <v>1.1737</v>
       </c>
       <c r="F8" t="n">
-        <v>1.88</v>
+        <v>-1.2652</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08690000000000001</v>
+        <v>-0.6569</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.038</v>
+        <v>-0.3298</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1248</v>
+        <v>-0.3271</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2315</v>
+        <v>0.8643</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.8509</v>
+        <v>1.3386</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6193</v>
+        <v>-0.4744</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3184</v>
+        <v>-1.5212</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1871</v>
+        <v>-1.6684</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5055</v>
+        <v>0.1472</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1716</v>
+        <v>-0.1982</v>
       </c>
       <c r="R8" t="n">
-        <v>1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3777</v>
+        <v>0.3056</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2898</v>
+        <v>-0.202</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2745</v>
+        <v>-0.5331</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0674</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3811</v>
+        <v>-1.5891</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2697</v>
+        <v>-0.3092</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1114</v>
+        <v>-1.2799</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0336</v>
@@ -1156,13 +1156,13 @@
         <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5851</v>
+        <v>0.3771</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3047</v>
+        <v>0.2653</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2803</v>
+        <v>0.1119</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1397</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6308</v>
+        <v>-2.4664</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3454</v>
+        <v>-3.4057</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7146</v>
+        <v>0.9393</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7519</v>
@@ -1234,13 +1234,13 @@
         <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2342</v>
+        <v>1.3986</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0586</v>
+        <v>0.8811</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2928</v>
+        <v>0.5174</v>
       </c>
       <c r="V10" t="n">
         <v>0.0674</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.254700000000003</v>
+        <v>10.1905</v>
       </c>
       <c r="E11" t="n">
-        <v>7.3636</v>
+        <v>8.299400000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8911</v>
+        <v>1.891</v>
       </c>
       <c r="G11" t="n">
-        <v>3.962700000000002</v>
+        <v>3.962700000000001</v>
       </c>
       <c r="H11" t="n">
         <v>-12.1656</v>
@@ -1285,13 +1285,13 @@
         <v>16.1281</v>
       </c>
       <c r="J11" t="n">
-        <v>8.0374</v>
+        <v>8.037400000000002</v>
       </c>
       <c r="K11" t="n">
         <v>-1.8646</v>
       </c>
       <c r="L11" t="n">
-        <v>9.9018</v>
+        <v>9.901800000000001</v>
       </c>
       <c r="M11" t="n">
         <v>-4.0749</v>
@@ -1312,19 +1312,19 @@
         <v>9.911099999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>7.305</v>
+        <v>8.2409</v>
       </c>
       <c r="T11" t="n">
-        <v>6.773999999999999</v>
+        <v>7.709899999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5309000000000001</v>
+        <v>0.5309</v>
       </c>
       <c r="V11" t="n">
         <v>1.9515</v>
       </c>
       <c r="W11" t="n">
-        <v>6.427900000000001</v>
+        <v>6.427899999999999</v>
       </c>
       <c r="X11" t="n">
         <v>-4.4763</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5316</v>
+        <v>3.3175</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1171</v>
+        <v>4.6078</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5855</v>
+        <v>-1.2903</v>
       </c>
       <c r="G12" t="n">
         <v>3.9686</v>
@@ -1390,13 +1390,13 @@
         <v>1.5858</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.765</v>
+        <v>-0.9792</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1837</v>
+        <v>-0.3256</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9488</v>
+        <v>-0.6536</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2666</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MUÑOZ MENDOZA</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3027</v>
+        <v>0.648</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3027</v>
+        <v>-1.105</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.753</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3027</v>
+        <v>-0.1488</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3027</v>
+        <v>0.5093</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0.6581</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3027</v>
+        <v>-0.8027</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3027</v>
+        <v>0.5517</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-1.3544</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.6538</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-0.0424</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.6962</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-1.2031</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.5183</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0.6848</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>J. MUÑOZ MENDOZA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2184</v>
+        <v>0.3027</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2069</v>
+        <v>0.3027</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4252</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1488</v>
+        <v>0.3027</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5093</v>
+        <v>0.3027</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6581</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8027</v>
+        <v>0.3027</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5517</v>
+        <v>0.3027</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3544</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6538</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0424</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6962</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6328</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6202</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0126</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. CASTRO BRAVO</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0472</v>
+        <v>0.269</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-0.8972</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0472</v>
+        <v>1.1662</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.066</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2018</v>
+        <v>1.1004</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1358</v>
+        <v>-2.0949</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.2915</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.3436</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.6351</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.066</v>
+        <v>-0.703</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2018</v>
+        <v>0.7569</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1358</v>
+        <v>-1.4599</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0187</v>
+        <v>-0.3817</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.2687</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0187</v>
+        <v>-0.113</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>S. CASTRO BRAVO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2563</v>
+        <v>-0.0192</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1593</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4156</v>
+        <v>-0.0192</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3304</v>
+        <v>-0.066</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5025</v>
+        <v>-0.2018</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8329</v>
+        <v>0.1358</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9954</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9553</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3258</v>
+        <v>-0.066</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5472</v>
+        <v>-0.2018</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8731</v>
+        <v>0.1358</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6865</v>
+        <v>0.0468</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1549</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4684</v>
+        <v>0.0468</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8914</v>
+        <v>-0.5722</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.814</v>
+        <v>-0.2837</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9226</v>
+        <v>-0.2885</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9945000000000001</v>
+        <v>0.438</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1004</v>
+        <v>2.6496</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0949</v>
+        <v>-2.2116</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2915</v>
+        <v>2.0551</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3436</v>
+        <v>2.2806</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6351</v>
+        <v>-0.2255</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.703</v>
+        <v>-1.6171</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7569</v>
+        <v>0.369</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4599</v>
+        <v>-1.9861</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9822</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9822</v>
+        <v>2.3787</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5421</v>
+        <v>-1.2857</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1855</v>
+        <v>-0.2356</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3566</v>
+        <v>-1.0501</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.337</v>
+        <v>0.8701</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.337</v>
+        <v>0.8701</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MUNOZ LEIVA</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0714</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0672</v>
+        <v>-0.2029</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1387</v>
+        <v>-0.7905</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4137</v>
+        <v>-2.1836</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4316</v>
+        <v>-1.3534</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0179</v>
+        <v>-0.8302</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6411</v>
+        <v>-0.5416</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6009</v>
+        <v>-1.0354</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>0.4938</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2274</v>
+        <v>-1.642</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8307</v>
+        <v>-0.318</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0581</v>
+        <v>-1.3241</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1413</v>
+        <v>-0.7305</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2458</v>
+        <v>-0.1944</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8955</v>
+        <v>-0.5361</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.7403</v>
+        <v>0.5331</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.337</v>
+        <v>0.5331</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>J. MUNOZ LEIVA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4662</v>
+        <v>-1.1204</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2029</v>
+        <v>-0.1365</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2633</v>
+        <v>-0.9839</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1836</v>
+        <v>1.4137</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3534</v>
+        <v>2.4316</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8302</v>
+        <v>-1.0179</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5416</v>
+        <v>1.6411</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0354</v>
+        <v>1.6009</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4938</v>
+        <v>0.0402</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.642</v>
+        <v>-0.2274</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.318</v>
+        <v>0.8307</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3241</v>
+        <v>-1.0581</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2033</v>
+        <v>-1.1903</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1944</v>
+        <v>-0.4495</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0088</v>
+        <v>-0.7408</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5331</v>
+        <v>-1.7403</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5331</v>
+        <v>-0.337</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.4033</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8495</v>
+        <v>-1.3325</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7931</v>
+        <v>0.835</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0564</v>
+        <v>-2.1674</v>
       </c>
       <c r="G20" t="n">
-        <v>0.438</v>
+        <v>-0.3304</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6496</v>
+        <v>1.5025</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2116</v>
+        <v>-1.8329</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0551</v>
+        <v>0.9954</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2806</v>
+        <v>0.9553</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2255</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6171</v>
+        <v>-1.3258</v>
       </c>
       <c r="N20" t="n">
-        <v>0.369</v>
+        <v>0.5472</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.9861</v>
+        <v>-1.8731</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3787</v>
+        <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.563</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.745</v>
+        <v>0.8306</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.818</v>
+        <v>-0.2203</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8701</v>
+        <v>-1.8107</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8532</v>
+        <v>-2.7784</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2591</v>
+        <v>-1.6479</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5942</v>
+        <v>-1.1305</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1649</v>
@@ -2092,13 +2092,13 @@
         <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2988</v>
+        <v>-0.2239</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4257</v>
+        <v>0.1855</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.873</v>
+        <v>-0.4094</v>
       </c>
       <c r="V21" t="n">
         <v>0.7997</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.872</v>
+        <v>-4.2592</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2614</v>
+        <v>-3.3633</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6106</v>
+        <v>-0.8959</v>
       </c>
       <c r="G22" t="n">
         <v>-4.1974</v>
@@ -2170,13 +2170,13 @@
         <v>1.3876</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1361</v>
+        <v>0.7489</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5471</v>
+        <v>0.4452</v>
       </c>
       <c r="U22" t="n">
-        <v>0.589</v>
+        <v>0.3036</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2071</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.2545</v>
+        <v>-6.5381</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.891100000000001</v>
+        <v>-1.891</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.3637</v>
+        <v>-4.647</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9626</v>
@@ -2221,7 +2221,7 @@
         <v>-16.128</v>
       </c>
       <c r="J23" t="n">
-        <v>4.074599999999999</v>
+        <v>4.0746</v>
       </c>
       <c r="K23" t="n">
         <v>10.3009</v>
@@ -2239,7 +2239,7 @@
         <v>-9.902100000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>3.9644</v>
+        <v>3.964399999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.911</v>
@@ -2248,13 +2248,13 @@
         <v>13.8757</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.305000000000001</v>
+        <v>-4.588299999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5308999999999998</v>
+        <v>-0.5308000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.774000000000001</v>
+        <v>-4.0577</v>
       </c>
       <c r="V23" t="n">
         <v>-1.9517</v>
@@ -2263,7 +2263,7 @@
         <v>4.476299999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.427900000000001</v>
+        <v>-6.427899999999999</v>
       </c>
     </row>
   </sheetData>
